--- a/output/pdf_financials_xlsx/CTH.xlsx
+++ b/output/pdf_financials_xlsx/CTH.xlsx
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.022562</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003781</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -2232,19 +2232,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.584789</v>
+        <v>-0.607351</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.016072</v>
+        <v>-1.019853</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.383</v>
+        <v>-3.417</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.998</v>
+        <v>-1.124</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.352</v>
+        <v>-5.404</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2366,19 +2366,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.584789</v>
+        <v>-0.607351</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.016072</v>
+        <v>-1.019853</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.382</v>
+        <v>-3.416</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.997</v>
+        <v>-1.123</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.352</v>
+        <v>-5.404</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-134.2026078234704</v>
+        <v>-135.506519558676</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
         <v>0.3</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.003</v>
@@ -2843,10 +2843,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.003</v>
@@ -3599,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -51898,7 +51898,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -52622,7 +52622,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -54590,7 +54590,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E432" s="5" t="n">

--- a/output/pdf_financials_xlsx/CTH.xlsx
+++ b/output/pdf_financials_xlsx/CTH.xlsx
@@ -1222,22 +1222,22 @@
         <v>-0</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>0.017</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>0.095</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>0.903</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>-0</v>
+        <v>2.492</v>
       </c>
     </row>
     <row r="14">
@@ -2274,22 +2274,22 @@
         <v>-0.09</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.103</v>
+        <v>-0.12</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.609</v>
+        <v>-0.61</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.451</v>
+        <v>1.391</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>9.619</v>
+        <v>9.523999999999999</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-8.009</v>
+        <v>-8.912000000000001</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-19.402</v>
+        <v>-21.894</v>
       </c>
     </row>
     <row r="28">
@@ -2408,22 +2408,22 @@
         <v>-0.09</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.103</v>
+        <v>-0.12</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.609</v>
+        <v>-0.61</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.451</v>
+        <v>1.391</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>9.619</v>
+        <v>9.523999999999999</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-8.009</v>
+        <v>-8.912000000000001</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-19.402</v>
+        <v>-21.894</v>
       </c>
     </row>
     <row r="30">
@@ -46546,7 +46546,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -50546,7 +50550,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
